--- a/Thesis_TSSP_NEW_M1_Results_25_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_25_Scenarios.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,17 +478,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -500,12 +500,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -515,17 +515,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -537,12 +537,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 06:25</t>
+          <t>4/5/2026 06:09</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -579,27 +579,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -611,17 +611,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 08:08</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:50</t>
+          <t>4/5/2026 12:29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -700,17 +700,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 10:12</t>
+          <t>4/5/2026 06:49</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 07:33</t>
         </is>
       </c>
     </row>
@@ -722,32 +722,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:41</t>
+          <t>4/5/2026 14:38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 14:09</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -769,22 +769,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 08:27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 13:08</t>
+          <t>4/5/2026 10:24</t>
         </is>
       </c>
     </row>
@@ -796,32 +796,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:34</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:27</t>
+          <t>4/5/2026 12:51</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 10:41</t>
+          <t>4/5/2026 12:17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 14:28</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 13:23</t>
+          <t>4/5/2026 14:19</t>
         </is>
       </c>
     </row>
@@ -870,22 +870,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 16:06</t>
+          <t>4/5/2026 08:26</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 08:50</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 08:29</t>
+          <t>4/5/2026 11:32</t>
         </is>
       </c>
     </row>
@@ -907,32 +907,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:41</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 10:17</t>
+          <t>4/5/2026 08:41</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 15:02</t>
         </is>
       </c>
     </row>
@@ -944,22 +944,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 10:22</t>
+          <t>4/5/2026 15:46</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 15:23</t>
+          <t>4/5/2026 06:35</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 14:54</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 15:41</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:09</t>
+          <t>4/5/2026 07:10</t>
         </is>
       </c>
     </row>
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 10:31</t>
+          <t>4/5/2026 14:25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 10:17</t>
+          <t>4/5/2026 15:46</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 15:57</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 13:47</t>
+          <t>4/5/2026 10:06</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 15:44</t>
+          <t>4/5/2026 15:21</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 15:25</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 11:04</t>
+          <t>4/5/2026 15:38</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 16:01</t>
+          <t>4/5/2026 12:58</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 13:31</t>
+          <t>4/5/2026 14:55</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 15:18</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:22</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:50</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 14:44</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 14:27</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1203,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 12:41</t>
+          <t>4/5/2026 14:49</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 13:49</t>
+          <t>4/5/2026 10:36</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 14:26</t>
+          <t>4/5/2026 11:30</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>439.56 min</t>
+          <t>427.68 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>34.42 min</t>
+          <t>30.97 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.72 min</t>
+          <t>86.00 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>139.00 min</t>
+          <t>121.00 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.00 min</t>
+          <t>16.20 min</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11.04/15.00/19.28 min</t>
+          <t>5.28/4.16/9.28 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2608413 / 163926</t>
+          <t>2499213 / 158926</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>270.3070 sec</t>
+          <t>228.7690 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.8955 %</t>
+          <t>0.3175 %</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>36.05 min | 94.00 min</t>
+          <t>32.10 min | 87.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32.86 min | 104.00 min</t>
+          <t>28.62 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35.67 min | 121.00 min</t>
+          <t>30.14 min | 81.00 min</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>35.52 min | 110.00 min</t>
+          <t>32.10 min | 79.00 min</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>32.14 min | 84.00 min</t>
+          <t>31.33 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>35.00 min | 121.00 min</t>
+          <t>32.43 min | 121.00 min</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>32.14 min | 100.00 min</t>
+          <t>29.29 min | 91.00 min</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>36.67 min | 128.00 min</t>
+          <t>31.10 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>35.38 min | 80.00 min</t>
+          <t>30.86 min | 80.00 min</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>33.29 min | 87.00 min</t>
+          <t>31.57 min | 91.00 min</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30.62 min | 83.00 min</t>
+          <t>29.24 min | 83.00 min</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>33.05 min | 84.00 min</t>
+          <t>27.86 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>35.62 min | 87.00 min</t>
+          <t>33.19 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>35.24 min | 105.00 min</t>
+          <t>28.81 min | 81.00 min</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>34.48 min | 88.00 min</t>
+          <t>32.57 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>34.10 min | 88.00 min</t>
+          <t>30.43 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>35.38 min | 118.00 min</t>
+          <t>31.48 min | 91.00 min</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>32.57 min | 88.00 min</t>
+          <t>31.05 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>39.52 min | 102.00 min</t>
+          <t>32.62 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>31.95 min | 115.00 min</t>
+          <t>29.67 min | 81.00 min</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>34.14 min | 114.00 min</t>
+          <t>30.76 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>35.81 min | 139.00 min</t>
+          <t>31.71 min | 82.00 min</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>32.24 min | 84.00 min</t>
+          <t>31.62 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>35.00 min | 105.00 min</t>
+          <t>31.90 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>36.19 min | 89.00 min</t>
+          <t>31.86 min | 77.00 min</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>15.99</v>
+        <v>16.44</v>
       </c>
     </row>
     <row r="56">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6.85</v>
+        <v>16.44</v>
       </c>
     </row>
     <row r="57">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9.140000000000001</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>15.99</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="59">
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="60">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="61">
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.07</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="62">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>32.16</v>
+        <v>28.93</v>
       </c>
     </row>
     <row r="63">
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>32.16</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="64">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>20.1</v>
+        <v>37.19</v>
       </c>
     </row>
   </sheetData>
@@ -2098,22 +2098,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:22</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4/5/2026 13:08</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2132,25 +2132,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:06</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:19</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:19</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:21</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -2158,22 +2158,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:21</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:28</t>
+          <t>4/5/2026 13:10</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2445,35 +2445,35 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 12:15</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4/5/2026 12:17</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4/5/2026 12:35</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2492,48 +2492,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4/5/2026 12:41</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 12:46</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 12:46</t>
+          <t>4/5/2026 12:58</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4/5/2026 13:08</t>
+          <t>4/5/2026 13:16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4/5/2026 13:37</t>
+          <t>4/5/2026 13:45</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="N10" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -2672,48 +2672,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:27</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:27</t>
+          <t>4/5/2026 11:39</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:47</t>
+          <t>4/5/2026 11:59</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -2745,35 +2745,35 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4/5/2026 11:58</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4/5/2026 12:35</t>
+          <t>4/5/2026 12:02</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="N14" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2912,16 +2912,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -3105,35 +3105,35 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 11:20</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4/5/2026 11:22</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4/5/2026 12:05</t>
+          <t>4/5/2026 11:39</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="N20" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3298,22 +3298,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 10:50</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:39</t>
+          <t>4/5/2026 11:20</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3358,22 +3358,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:32</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4/5/2026 13:18</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="N24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3418,22 +3418,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:13</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:20</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3825,35 +3825,35 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:38</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4/5/2026 08:41</t>
+          <t>4/5/2026 08:39</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4/5/2026 09:01</t>
+          <t>4/5/2026 08:39</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="N32" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4018,22 +4018,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="N35" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4172,25 +4172,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -4198,22 +4198,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -4592,48 +4592,48 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4/5/2026 12:24</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4/5/2026 12:28</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4/5/2026 12:29</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>4/5/2026 13:35</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="N45" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M47" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -5252,48 +5252,48 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 11:03</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>4/5/2026 11:22</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4/5/2026 11:44</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>4/5/2026 12:04</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>4/5/2026 12:41</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="N56" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5518,22 +5518,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -5578,22 +5578,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:48</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>4/5/2026 10:08</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="N61" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5685,35 +5685,35 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>4/5/2026 09:48</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="N63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -6452,25 +6452,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:30</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 12:03</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M76" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77">
@@ -6512,48 +6512,48 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:03</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="N77" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6932,48 +6932,48 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:35</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>4/5/2026 13:04</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4/5/2026 13:12</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 12:47</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 12:47</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>4/5/2026 13:45</t>
+          <t>4/5/2026 13:17</t>
         </is>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="N84" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -7198,22 +7198,22 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:21</t>
+          <t>4/5/2026 13:10</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="N88" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7245,35 +7245,35 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4/5/2026 10:16</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>4/5/2026 10:23</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="N89" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -7472,48 +7472,48 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>4/5/2026 10:11</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -7545,35 +7545,35 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:44</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="L94" t="n">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -7952,25 +7952,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -7987,7 +7987,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
         <v>24</v>
@@ -8312,48 +8312,48 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4/5/2026 08:52</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>4/5/2026 08:52</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 10:10</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M107" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108">
@@ -8372,42 +8372,42 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>4/5/2026 10:08</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
+          <t>4/5/2026 09:57</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
           <t>4/5/2026 10:10</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>10</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>4/5/2026 10:10</t>
-        </is>
-      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M108" t="n">
         <v>121</v>
@@ -8518,22 +8518,22 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 11:49</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -8818,22 +8818,22 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>4/5/2026 11:14</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="N115" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -8972,25 +8972,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:20</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>4/5/2026 11:21</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4/5/2026 11:21</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:30</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -8998,22 +8998,22 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>4/5/2026 11:32</t>
+          <t>4/5/2026 11:40</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M118" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N118" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119">
@@ -9032,48 +9032,48 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>4/5/2026 10:13</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="N119" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -9358,22 +9358,22 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>4/5/2026 09:52</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>4/5/2026 10:12</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="N124" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -9452,25 +9452,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>4/5/2026 11:37</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:57</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:57</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -9478,22 +9478,22 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>4/5/2026 12:24</t>
+          <t>4/5/2026 12:30</t>
         </is>
       </c>
       <c r="L126" t="n">
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127">
@@ -9598,22 +9598,22 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 12:19</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M128" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129">
@@ -9658,22 +9658,22 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>4/5/2026 12:28</t>
+          <t>4/5/2026 12:19</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M129" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="N129" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130">
@@ -9718,22 +9718,22 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>4/5/2026 13:09</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M130" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -9778,22 +9778,22 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 11:51</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="N131" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -10605,35 +10605,35 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>4/5/2026 10:07</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>4/5/2026 10:27</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="N145" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -10738,22 +10738,22 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>4/5/2026 10:27</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>4/5/2026 10:51</t>
+          <t>4/5/2026 10:40</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="N147" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -10892,48 +10892,48 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>4/5/2026 11:36</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
+          <t>4/5/2026 12:12</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:12</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
           <t>4/5/2026 12:14</t>
         </is>
       </c>
-      <c r="F150" t="n">
-        <v>2</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:34</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:36</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>4/5/2026 13:42</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="N150" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -10978,22 +10978,22 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>4/5/2026 13:06</t>
+          <t>4/5/2026 13:07</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -11038,22 +11038,22 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 13:07</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>4/5/2026 13:22</t>
+          <t>4/5/2026 13:34</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M152" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153">
@@ -11312,48 +11312,48 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:58</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>4/5/2026 08:42</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>4/5/2026 08:54</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N157" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="158">
@@ -11372,48 +11372,48 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:33</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>4/5/2026 08:44</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>4/5/2026 08:44</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
+          <t>4/5/2026 08:41</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>4/5/2026 08:41</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t>4/5/2026 08:45</t>
         </is>
       </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:03</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:07</t>
-        </is>
-      </c>
       <c r="L158" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="N158" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -11565,35 +11565,35 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t>4/5/2026 08:47</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t>4/5/2026 09:15</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:43</t>
-        </is>
-      </c>
       <c r="L161" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="N161" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -11732,48 +11732,48 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L164" t="n">
         <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="N164" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -11818,22 +11818,22 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N165" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -11865,35 +11865,35 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>4/5/2026 12:46</t>
+          <t>4/5/2026 12:45</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>4/5/2026 13:06</t>
+          <t>4/5/2026 12:45</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>4/5/2026 13:35</t>
+          <t>4/5/2026 13:14</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="N166" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -12092,48 +12092,48 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 10:03</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M170" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="171">
@@ -12272,48 +12272,48 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="N173" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -12538,22 +12538,22 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>4/5/2026 12:17</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>4/5/2026 12:41</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -12598,22 +12598,22 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>4/5/2026 13:23</t>
+          <t>4/5/2026 13:17</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="N178" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -12752,48 +12752,48 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
+          <t>4/5/2026 11:33</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
           <t>4/5/2026 11:35</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:37</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 11:38</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>4/5/2026 12:17</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M181" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="N181" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182">
@@ -12992,25 +12992,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="I185" t="n">
@@ -13018,22 +13018,22 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:46</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:55</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="N185" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -13172,48 +13172,48 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>4/5/2026 11:03</t>
+          <t>4/5/2026 11:02</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
+          <t>4/5/2026 11:14</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:14</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
           <t>4/5/2026 11:15</t>
         </is>
       </c>
-      <c r="F188" t="n">
-        <v>1</v>
-      </c>
-      <c r="G188" t="inlineStr">
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="inlineStr">
         <is>
           <t>4/5/2026 11:15</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:16</t>
-        </is>
-      </c>
-      <c r="I188" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:26</t>
-        </is>
-      </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:38</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="N188" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -13245,35 +13245,35 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>4/5/2026 11:38</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>4/5/2026 11:40</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M189" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="N189" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="190">
@@ -13352,25 +13352,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:38</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 11:46</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 11:46</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>4/5/2026 11:59</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="I191" t="n">
@@ -13378,22 +13378,22 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>4/5/2026 12:39</t>
+          <t>4/5/2026 12:19</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M191" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="N191" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="192">
@@ -13438,22 +13438,22 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:15</t>
+          <t>4/5/2026 12:19</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>4/5/2026 13:01</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M192" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="193">
@@ -13498,22 +13498,22 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>4/5/2026 13:06</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M193" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194">
@@ -13772,48 +13772,48 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M198" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199">
@@ -14012,48 +14012,48 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:29</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:39</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>4/5/2026 12:16</t>
+          <t>4/5/2026 11:45</t>
         </is>
       </c>
       <c r="L202" t="n">
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="N202" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -14252,48 +14252,48 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:18</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:19</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:21</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:30</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>2</v>
+      </c>
+      <c r="M206" t="n">
+        <v>21</v>
+      </c>
+      <c r="N206" t="n">
         <v>3</v>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:24</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:25</t>
-        </is>
-      </c>
-      <c r="I206" t="n">
-        <v>4</v>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:25</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:34</t>
-        </is>
-      </c>
-      <c r="L206" t="n">
-        <v>0</v>
-      </c>
-      <c r="M206" t="n">
-        <v>25</v>
-      </c>
-      <c r="N206" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="207">
@@ -14312,25 +14312,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I207" t="n">
@@ -14338,22 +14338,22 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L207" t="n">
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N207" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -14372,48 +14372,48 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:41</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>4/5/2026 10:03</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N208" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -14432,48 +14432,48 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>4/5/2026 09:01</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 08:59</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M209" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N209" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="210">
@@ -14505,35 +14505,35 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>4/5/2026 11:39</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:45</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M210" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211">
@@ -15585,35 +15585,35 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="I228" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>4/5/2026 09:44</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>4/5/2026 09:52</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="L228" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="N228" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -16078,22 +16078,22 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 09:58</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>4/5/2026 10:21</t>
+          <t>4/5/2026 10:05</t>
         </is>
       </c>
       <c r="L236" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="N236" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -16832,48 +16832,48 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="I249" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>4/5/2026 09:46</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="L249" t="n">
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="N249" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -16905,35 +16905,35 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:43</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:45</t>
         </is>
       </c>
       <c r="I250" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 12:45</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>4/5/2026 13:44</t>
+          <t>4/5/2026 13:14</t>
         </is>
       </c>
       <c r="L250" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="N250" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -16965,35 +16965,35 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>4/5/2026 12:25</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>4/5/2026 12:27</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="I251" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>4/5/2026 12:42</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>4/5/2026 13:10</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="L251" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="N251" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -17072,48 +17072,48 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4/5/2026 08:59</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
+          <t>4/5/2026 09:05</t>
+        </is>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:05</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t>4/5/2026 09:08</t>
         </is>
       </c>
-      <c r="I253" t="n">
-        <v>0</v>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:08</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:11</t>
-        </is>
-      </c>
       <c r="L253" t="n">
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N253" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -17278,22 +17278,22 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>4/5/2026 13:04</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>4/5/2026 13:11</t>
+          <t>4/5/2026 13:06</t>
         </is>
       </c>
       <c r="L256" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N256" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -17312,48 +17312,48 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>4/5/2026 13:01</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>4/5/2026 13:04</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:53</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:55</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>4/5/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>4/5/2026 13:33</t>
+        </is>
+      </c>
+      <c r="L257" t="n">
         <v>11</v>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:12</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:14</t>
-        </is>
-      </c>
-      <c r="I257" t="n">
-        <v>8</v>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:14</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:41</t>
-        </is>
-      </c>
-      <c r="L257" t="n">
-        <v>0</v>
-      </c>
       <c r="M257" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N257" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="258">
@@ -17552,25 +17552,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="I261" t="n">
@@ -17578,22 +17578,22 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:36</t>
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M261" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="262">
@@ -18032,42 +18032,42 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="F269" t="n">
+        <v>1</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:17</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:19</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:21</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:30</t>
+        </is>
+      </c>
+      <c r="L269" t="n">
         <v>2</v>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:19</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:21</t>
-        </is>
-      </c>
-      <c r="I269" t="n">
-        <v>1</v>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:21</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:30</t>
-        </is>
-      </c>
-      <c r="L269" t="n">
-        <v>0</v>
       </c>
       <c r="M269" t="n">
         <v>21</v>
@@ -18178,22 +18178,22 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>4/5/2026 10:02</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="L271" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N271" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -18238,22 +18238,22 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="L272" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M272" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N272" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="273">
@@ -18272,48 +18272,48 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:37</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 11:47</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 11:47</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>4/5/2026 12:15</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="I273" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>4/5/2026 12:34</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>4/5/2026 13:04</t>
+          <t>4/5/2026 12:20</t>
         </is>
       </c>
       <c r="L273" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="N273" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -18465,35 +18465,35 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>4/5/2026 12:13</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="I276" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>4/5/2026 12:33</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>4/5/2026 13:19</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="L276" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="N276" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -18585,16 +18585,16 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="I278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M278" t="n">
         <v>12</v>
@@ -18825,35 +18825,35 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>4/5/2026 12:32</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>4/5/2026 12:34</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="I282" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>4/5/2026 13:18</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="L282" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="N282" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -18885,35 +18885,35 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 12:46</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>4/5/2026 13:04</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="I283" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>4/5/2026 13:19</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>4/5/2026 13:48</t>
+          <t>4/5/2026 13:17</t>
         </is>
       </c>
       <c r="L283" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="N283" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -19065,35 +19065,35 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:22</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
+          <t>4/5/2026 11:24</t>
+        </is>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:24</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t>4/5/2026 11:44</t>
         </is>
       </c>
-      <c r="I286" t="n">
-        <v>20</v>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:59</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:19</t>
-        </is>
-      </c>
       <c r="L286" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="N286" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -19258,22 +19258,22 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>4/5/2026 10:52</t>
+          <t>4/5/2026 10:44</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>4/5/2026 11:01</t>
+          <t>4/5/2026 10:53</t>
         </is>
       </c>
       <c r="L289" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M289" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N289" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -19378,22 +19378,22 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M291" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -19665,35 +19665,35 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>4/5/2026 10:48</t>
+          <t>4/5/2026 10:45</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 10:46</t>
         </is>
       </c>
       <c r="I296" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 10:46</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>4/5/2026 11:39</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="L296" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="N296" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -19832,48 +19832,48 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
+          <t>4/5/2026 12:53</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:55</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:57</t>
+        </is>
+      </c>
+      <c r="I299" t="n">
+        <v>2</v>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
           <t>4/5/2026 13:02</t>
         </is>
       </c>
-      <c r="F299" t="n">
-        <v>9</v>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:06</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:08</t>
-        </is>
-      </c>
-      <c r="I299" t="n">
-        <v>4</v>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:15</t>
-        </is>
-      </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>4/5/2026 13:42</t>
+          <t>4/5/2026 13:29</t>
         </is>
       </c>
       <c r="L299" t="n">
+        <v>5</v>
+      </c>
+      <c r="M299" t="n">
+        <v>39</v>
+      </c>
+      <c r="N299" t="n">
         <v>7</v>
-      </c>
-      <c r="M299" t="n">
-        <v>52</v>
-      </c>
-      <c r="N299" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="300">
@@ -19918,22 +19918,22 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="L300" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N300" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -20385,35 +20385,35 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>4/5/2026 08:50</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="I308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>4/5/2026 08:50</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="L308" t="n">
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -20578,22 +20578,22 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L311" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M311" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N311" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="312">
@@ -20792,48 +20792,48 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>4/5/2026 08:32</t>
+          <t>4/5/2026 08:36</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>4/5/2026 08:44</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>4/5/2026 08:44</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="I315" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M315" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="N315" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="316">
@@ -20878,22 +20878,22 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="L316" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="N316" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -20938,22 +20938,22 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 10:58</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:32</t>
         </is>
       </c>
       <c r="L317" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="N317" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -21118,22 +21118,22 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="L320" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="N320" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -21405,35 +21405,35 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:46</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="I325" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>4/5/2026 13:44</t>
+          <t>4/5/2026 13:17</t>
         </is>
       </c>
       <c r="L325" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="N325" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -21478,22 +21478,22 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 08:41</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="L326" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="N326" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -21645,35 +21645,35 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:20</t>
         </is>
       </c>
       <c r="I329" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:32</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>4/5/2026 12:20</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="L329" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M329" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N329" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="330">
@@ -21812,25 +21812,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="I332" t="n">
@@ -21847,7 +21847,7 @@
         </is>
       </c>
       <c r="L332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M332" t="n">
         <v>21</v>
@@ -22065,35 +22065,35 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
+          <t>4/5/2026 11:51</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
           <t>4/5/2026 11:53</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:55</t>
-        </is>
-      </c>
       <c r="I336" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>4/5/2026 12:25</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="L336" t="n">
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N336" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -22172,48 +22172,48 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F338" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="I338" t="n">
+        <v>10</v>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:23</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>4/5/2026 10:16</t>
+        </is>
+      </c>
+      <c r="L338" t="n">
         <v>15</v>
       </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:50</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>4/5/2026 10:43</t>
-        </is>
-      </c>
-      <c r="L338" t="n">
-        <v>20</v>
-      </c>
       <c r="M338" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="N338" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="339">
@@ -22352,48 +22352,48 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 08:58</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="I341" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="L341" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M341" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N341" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="342">
@@ -22618,22 +22618,22 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>4/5/2026 10:43</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>4/5/2026 11:12</t>
+          <t>4/5/2026 11:07</t>
         </is>
       </c>
       <c r="L345" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M345" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N345" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -22918,22 +22918,22 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="L350" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M350" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="N350" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -23072,48 +23072,48 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="I353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="L353" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M353" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="N353" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="354">
@@ -23158,22 +23158,22 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="L354" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="N354" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -23205,35 +23205,35 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
+          <t>4/5/2026 09:34</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
           <t>4/5/2026 09:37</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:40</t>
-        </is>
-      </c>
       <c r="I355" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>4/5/2026 10:03</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="L355" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M355" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N355" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
@@ -23265,35 +23265,35 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>4/5/2026 10:17</t>
+          <t>4/5/2026 10:11</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>4/5/2026 10:20</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="I356" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>4/5/2026 10:40</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>4/5/2026 11:07</t>
+          <t>4/5/2026 10:41</t>
         </is>
       </c>
       <c r="L356" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M356" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="N356" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -23325,35 +23325,35 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>4/5/2026 11:37</t>
+          <t>4/5/2026 11:45</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>4/5/2026 11:40</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="I357" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>4/5/2026 11:40</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>4/5/2026 12:05</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="L357" t="n">
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="N357" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="358">
@@ -23612,25 +23612,25 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="I362" t="n">
@@ -23638,22 +23638,22 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>4/5/2026 13:21</t>
+          <t>4/5/2026 13:29</t>
         </is>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M362" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="N362" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="363">
@@ -23852,25 +23852,25 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="F366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="I366" t="n">
@@ -23878,22 +23878,22 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="L366" t="n">
         <v>0</v>
       </c>
       <c r="M366" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -24092,25 +24092,25 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:29</t>
         </is>
       </c>
       <c r="F370" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:29</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:31</t>
         </is>
       </c>
       <c r="I370" t="n">
@@ -24118,22 +24118,22 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:40</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="L370" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M370" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="N370" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="371">
@@ -24165,35 +24165,35 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="I371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="L371" t="n">
         <v>0</v>
       </c>
       <c r="M371" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
@@ -24345,35 +24345,35 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="I374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>4/5/2026 09:44</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>4/5/2026 09:53</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="L374" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M374" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="N374" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375">
@@ -24572,48 +24572,48 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:35</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 12:43</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>4/5/2026 13:12</t>
+          <t>4/5/2026 12:43</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 12:45</t>
         </is>
       </c>
       <c r="I378" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 12:45</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>4/5/2026 13:44</t>
+          <t>4/5/2026 13:15</t>
         </is>
       </c>
       <c r="L378" t="n">
         <v>0</v>
       </c>
       <c r="M378" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="N378" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -24752,25 +24752,25 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>4/5/2026 12:28</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="F381" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>4/5/2026 12:28</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>4/5/2026 12:30</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="I381" t="n">
@@ -24778,22 +24778,22 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>4/5/2026 12:30</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>4/5/2026 13:16</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="L381" t="n">
         <v>0</v>
       </c>
       <c r="M381" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="N381" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -24958,22 +24958,22 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L384" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M384" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="N384" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -25138,22 +25138,22 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>4/5/2026 12:26</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="L387" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M387" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="N387" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -25352,48 +25352,48 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
+          <t>4/5/2026 12:23</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
           <t>4/5/2026 12:34</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:45</t>
-        </is>
-      </c>
       <c r="F391" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 12:34</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="I391" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>4/5/2026 13:45</t>
+          <t>4/5/2026 13:07</t>
         </is>
       </c>
       <c r="L391" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="N391" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -25425,35 +25425,35 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:15</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>4/5/2026 11:30</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
       <c r="I392" t="n">
+        <v>2</v>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:32</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:09</t>
+        </is>
+      </c>
+      <c r="L392" t="n">
         <v>15</v>
       </c>
-      <c r="J392" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:49</t>
-        </is>
-      </c>
-      <c r="K392" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:26</t>
-        </is>
-      </c>
-      <c r="L392" t="n">
-        <v>19</v>
-      </c>
       <c r="M392" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="N392" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="393">
@@ -25725,35 +25725,35 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>4/5/2026 09:41</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I397" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>4/5/2026 10:01</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>4/5/2026 10:21</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="L397" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M397" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="N397" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -25832,16 +25832,16 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -25854,26 +25854,26 @@
         </is>
       </c>
       <c r="I399" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>4/5/2026 10:01</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="L399" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M399" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N399" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="400">
@@ -25918,22 +25918,22 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="L400" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M400" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="N400" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -26025,35 +26025,35 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>4/5/2026 12:22</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>4/5/2026 12:23</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="I402" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>4/5/2026 13:29</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="L402" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M402" t="n">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="N402" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -26865,35 +26865,35 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="I416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L416" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M416" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="N416" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -26912,25 +26912,25 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="I417" t="n">
@@ -26938,22 +26938,22 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="L417" t="n">
         <v>0</v>
       </c>
       <c r="M417" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N417" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418">
@@ -27045,35 +27045,35 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
+          <t>4/5/2026 11:18</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
           <t>4/5/2026 11:20</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>4/5/2026 11:22</t>
-        </is>
-      </c>
       <c r="I419" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>4/5/2026 11:22</t>
+          <t>4/5/2026 11:20</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="L419" t="n">
         <v>0</v>
       </c>
       <c r="M419" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N419" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -27118,22 +27118,22 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="L420" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M420" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N420" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="421">
@@ -27238,22 +27238,22 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>4/5/2026 11:04</t>
+          <t>4/5/2026 10:51</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:21</t>
         </is>
       </c>
       <c r="L422" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M422" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="N422" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -27285,35 +27285,35 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>4/5/2026 12:20</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>4/5/2026 12:22</t>
+          <t>4/5/2026 12:12</t>
         </is>
       </c>
       <c r="I423" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>4/5/2026 12:42</t>
+          <t>4/5/2026 12:12</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>4/5/2026 13:28</t>
+          <t>4/5/2026 12:58</t>
         </is>
       </c>
       <c r="L423" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M423" t="n">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="N423" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424">
@@ -27692,48 +27692,48 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="I430" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="L430" t="n">
         <v>0</v>
       </c>
       <c r="M430" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="N430" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="431">
@@ -27752,48 +27752,48 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:33</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>4/5/2026 08:42</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 08:41</t>
         </is>
       </c>
       <c r="I431" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 08:41</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="L431" t="n">
         <v>0</v>
       </c>
       <c r="M431" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="N431" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -27945,35 +27945,35 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>4/5/2026 08:54</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="I434" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L434" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M434" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="N434" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435">
@@ -28125,35 +28125,35 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="I437" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N437" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -28185,35 +28185,35 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
+          <t>4/5/2026 09:12</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
           <t>4/5/2026 09:14</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:16</t>
-        </is>
-      </c>
       <c r="I438" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="L438" t="n">
         <v>0</v>
       </c>
       <c r="M438" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N438" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439">
@@ -28472,25 +28472,25 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>4/5/2026 10:55</t>
+          <t>4/5/2026 10:43</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 10:56</t>
         </is>
       </c>
       <c r="F443" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 10:56</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="I443" t="n">
@@ -28498,22 +28498,22 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:31</t>
         </is>
       </c>
       <c r="L443" t="n">
         <v>0</v>
       </c>
       <c r="M443" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N443" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444">
@@ -28532,48 +28532,48 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>4/5/2026 12:28</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="F444" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>4/5/2026 12:47</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="I444" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>4/5/2026 13:53</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="L444" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M444" t="n">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="N444" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445">
@@ -28665,35 +28665,35 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:54</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="I446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>4/5/2026 13:22</t>
+          <t>4/5/2026 13:23</t>
         </is>
       </c>
       <c r="L446" t="n">
         <v>0</v>
       </c>
       <c r="M446" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -29158,22 +29158,22 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:05</t>
         </is>
       </c>
       <c r="L454" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M454" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N454" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -29385,16 +29385,16 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="I458" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J458" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         </is>
       </c>
       <c r="L458" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M458" t="n">
         <v>23</v>
@@ -29505,35 +29505,35 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>4/5/2026 13:04</t>
+          <t>4/5/2026 12:46</t>
         </is>
       </c>
       <c r="I460" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>4/5/2026 13:24</t>
+          <t>4/5/2026 12:46</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>4/5/2026 13:53</t>
+          <t>4/5/2026 13:15</t>
         </is>
       </c>
       <c r="L460" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M460" t="n">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="N460" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="461">
@@ -29612,48 +29612,48 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:40</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>4/5/2026 11:40</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="F462" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>4/5/2026 11:40</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="I462" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 12:05</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>4/5/2026 12:08</t>
+          <t>4/5/2026 12:30</t>
         </is>
       </c>
       <c r="L462" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M462" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N462" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="463">
@@ -30212,48 +30212,48 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>4/5/2026 12:42</t>
+          <t>4/5/2026 12:43</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>4/5/2026 12:47</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>4/5/2026 12:51</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="I472" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 13:10</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>4/5/2026 13:27</t>
+          <t>4/5/2026 13:39</t>
         </is>
       </c>
       <c r="L472" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M472" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="N472" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="473">
@@ -30418,22 +30418,22 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>4/5/2026 12:40</t>
+          <t>4/5/2026 12:39</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>4/5/2026 13:11</t>
+          <t>4/5/2026 13:10</t>
         </is>
       </c>
       <c r="L475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M475" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="476">
@@ -30645,16 +30645,16 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="I479" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J479" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         </is>
       </c>
       <c r="L479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M479" t="n">
         <v>24</v>
@@ -30765,35 +30765,35 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>4/5/2026 12:46</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>4/5/2026 12:48</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="I481" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>4/5/2026 13:08</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>4/5/2026 13:37</t>
+          <t>4/5/2026 13:13</t>
         </is>
       </c>
       <c r="L481" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M481" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="N481" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482">
@@ -30992,48 +30992,48 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="F485" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="I485" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>4/5/2026 10:30</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="L485" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M485" t="n">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="N485" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="486">
@@ -31078,22 +31078,22 @@
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>4/5/2026 12:17</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="L486" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N486" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="487">
@@ -31905,29 +31905,29 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
         <is>
+          <t>4/5/2026 09:21</t>
+        </is>
+      </c>
+      <c r="I500" t="n">
+        <v>1</v>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
           <t>4/5/2026 09:24</t>
         </is>
       </c>
-      <c r="I500" t="n">
-        <v>4</v>
-      </c>
-      <c r="J500" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:24</t>
-        </is>
-      </c>
       <c r="K500" t="inlineStr">
         <is>
           <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="L500" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M500" t="n">
         <v>24</v>
@@ -32038,22 +32038,22 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>4/5/2026 09:49</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>4/5/2026 10:09</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="L502" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M502" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N502" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="503">
@@ -32098,22 +32098,22 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 08:59</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="L503" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M503" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="N503" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="504">
@@ -32518,22 +32518,22 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L510" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N510" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="511">
@@ -32672,48 +32672,48 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:46</t>
         </is>
       </c>
       <c r="F513" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>4/5/2026 09:44</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="I513" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>4/5/2026 10:04</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>4/5/2026 10:45</t>
+          <t>4/5/2026 10:36</t>
         </is>
       </c>
       <c r="L513" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M513" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="N513" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="514">
@@ -33272,48 +33272,48 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>4/5/2026 09:44</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="F523" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>4/5/2026 10:04</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>4/5/2026 10:06</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="I523" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>4/5/2026 10:25</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>4/5/2026 10:45</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="L523" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="N523" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
@@ -33332,48 +33332,48 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>4/5/2026 09:01</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="F524" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="I524" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>4/5/2026 09:52</t>
+          <t>4/5/2026 09:48</t>
         </is>
       </c>
       <c r="L524" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M524" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N524" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="525">
@@ -33452,48 +33452,48 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
+          <t>4/5/2026 09:03</t>
+        </is>
+      </c>
+      <c r="F526" t="n">
+        <v>0</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:03</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
           <t>4/5/2026 09:05</t>
         </is>
       </c>
-      <c r="F526" t="n">
-        <v>2</v>
-      </c>
-      <c r="G526" t="inlineStr">
+      <c r="I526" t="n">
+        <v>0</v>
+      </c>
+      <c r="J526" t="inlineStr">
         <is>
           <t>4/5/2026 09:05</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:07</t>
-        </is>
-      </c>
-      <c r="I526" t="n">
-        <v>0</v>
-      </c>
-      <c r="J526" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:23</t>
-        </is>
-      </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="L526" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="N526" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
